--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_002.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_002.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="183">
   <si>
     <t>Sezione</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
   </si>
   <si>
     <t>Provincia AIRE</t>
@@ -613,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -1369,7 +1375,7 @@
         <v>72</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>60</v>
@@ -1984,19 +1990,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="C60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -2007,19 +2013,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -2030,19 +2036,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2053,19 +2059,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2076,19 +2082,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2099,19 +2105,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2122,19 +2128,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2145,19 +2151,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2168,19 +2174,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2191,19 +2197,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2214,19 +2220,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2237,19 +2243,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2260,19 +2266,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2283,19 +2289,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2306,19 +2312,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2329,19 +2335,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2352,19 +2358,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2375,19 +2381,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2398,19 +2404,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2421,19 +2427,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2444,19 +2450,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2467,19 +2473,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2490,19 +2496,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2513,19 +2519,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2536,19 +2542,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2559,19 +2565,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2582,19 +2588,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2605,19 +2611,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2628,19 +2634,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2651,19 +2657,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2674,19 +2680,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2697,19 +2703,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2720,19 +2726,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2746,16 +2752,16 @@
         <v>127</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2769,16 +2775,16 @@
         <v>127</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2789,19 +2795,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2812,19 +2818,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2835,19 +2841,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2858,19 +2864,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2881,19 +2887,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2904,19 +2910,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2927,19 +2933,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2950,19 +2956,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2973,19 +2979,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2996,19 +3002,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3019,19 +3025,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3042,19 +3048,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3065,19 +3071,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3088,19 +3094,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3111,19 +3117,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3134,19 +3140,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3157,19 +3163,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3180,19 +3186,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3203,19 +3209,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3226,19 +3232,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3249,19 +3255,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3272,19 +3278,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3295,19 +3301,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3318,19 +3324,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3344,16 +3350,16 @@
         <v>155</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="E119" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3367,16 +3373,16 @@
         <v>155</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3387,19 +3393,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3410,19 +3416,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3433,19 +3439,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3456,19 +3462,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3479,19 +3485,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3502,19 +3508,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3525,19 +3531,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3548,19 +3554,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3571,19 +3577,19 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D129" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
@@ -3594,19 +3600,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3617,19 +3623,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3640,19 +3646,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3663,19 +3669,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3686,19 +3692,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3709,19 +3715,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
@@ -3732,19 +3738,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3755,24 +3761,70 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E137" s="2" t="s">
+      <c r="C138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G137" s="2" t="s">
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>27</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_002.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_002.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="187">
   <si>
     <t>Sezione</t>
   </si>
@@ -119,10 +119,22 @@
     <t>Dati della trascrizione</t>
   </si>
   <si>
+    <t>Formato Data Evento Matrimonio</t>
+  </si>
+  <si>
+    <t>evento.datiEventoMatrimonio</t>
+  </si>
+  <si>
+    <t>idFormatoDataEvento</t>
+  </si>
+  <si>
+    <t>Formato Data Evento Matrimonio - Descrizione</t>
+  </si>
+  <si>
+    <t>formatoDataEvento</t>
+  </si>
+  <si>
     <t>Data Evento Matrimonio</t>
-  </si>
-  <si>
-    <t>evento.datiEventoMatrimonio</t>
   </si>
   <si>
     <t>dataEvento</t>
@@ -619,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -1007,7 +1019,7 @@
         <v>35</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -1030,13 +1042,13 @@
         <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -1050,16 +1062,16 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -1073,13 +1085,13 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>44</v>
@@ -1102,7 +1114,7 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>46</v>
@@ -1125,7 +1137,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>48</v>
@@ -1148,7 +1160,7 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>50</v>
@@ -1171,7 +1183,7 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>52</v>
@@ -1194,10 +1206,10 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
@@ -1211,16 +1223,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1231,19 +1243,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1254,19 +1266,19 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1277,16 +1289,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>65</v>
@@ -1300,7 +1312,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>66</v>
@@ -1309,7 +1321,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>67</v>
@@ -1323,7 +1335,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>68</v>
@@ -1332,7 +1344,7 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>69</v>
@@ -1346,16 +1358,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>71</v>
@@ -1369,7 +1381,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
@@ -1378,7 +1390,7 @@
         <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>73</v>
@@ -1392,7 +1404,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
@@ -1401,7 +1413,7 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>75</v>
@@ -1415,7 +1427,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
@@ -1424,7 +1436,7 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>77</v>
@@ -1438,7 +1450,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
@@ -1447,7 +1459,7 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>79</v>
@@ -1461,7 +1473,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
@@ -1470,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>81</v>
@@ -1484,7 +1496,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
@@ -1493,7 +1505,7 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>83</v>
@@ -1507,7 +1519,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
@@ -1516,7 +1528,7 @@
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>85</v>
@@ -1530,19 +1542,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1553,19 +1565,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1576,16 +1588,16 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>90</v>
@@ -1599,7 +1611,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>91</v>
@@ -1608,7 +1620,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>92</v>
@@ -1622,7 +1634,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>93</v>
@@ -1631,7 +1643,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>94</v>
@@ -1645,7 +1657,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>95</v>
@@ -1654,7 +1666,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>96</v>
@@ -1668,7 +1680,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>97</v>
@@ -1677,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>98</v>
@@ -1691,7 +1703,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>99</v>
@@ -1700,7 +1712,7 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>100</v>
@@ -1714,7 +1726,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>101</v>
@@ -1723,7 +1735,7 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>102</v>
@@ -1737,7 +1749,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>103</v>
@@ -1746,7 +1758,7 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>104</v>
@@ -1760,7 +1772,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>105</v>
@@ -1769,7 +1781,7 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>106</v>
@@ -1783,7 +1795,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>107</v>
@@ -1792,7 +1804,7 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>108</v>
@@ -1806,16 +1818,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>110</v>
@@ -1829,16 +1841,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>112</v>
@@ -1852,7 +1864,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>113</v>
@@ -1861,7 +1873,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>114</v>
@@ -1875,16 +1887,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>116</v>
@@ -1898,16 +1910,16 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>118</v>
@@ -1921,7 +1933,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>119</v>
@@ -1930,7 +1942,7 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>120</v>
@@ -1944,7 +1956,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>121</v>
@@ -1953,7 +1965,7 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>122</v>
@@ -1967,7 +1979,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>123</v>
@@ -1976,7 +1988,7 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>124</v>
@@ -1990,7 +2002,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>125</v>
@@ -1999,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>126</v>
@@ -2013,19 +2025,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="C61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -2036,19 +2048,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2059,16 +2071,16 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>65</v>
@@ -2082,7 +2094,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>66</v>
@@ -2091,7 +2103,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>67</v>
@@ -2105,7 +2117,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>68</v>
@@ -2114,7 +2126,7 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>69</v>
@@ -2128,16 +2140,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>71</v>
@@ -2151,7 +2163,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>72</v>
@@ -2160,7 +2172,7 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>73</v>
@@ -2174,7 +2186,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>74</v>
@@ -2183,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>75</v>
@@ -2197,7 +2209,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>76</v>
@@ -2206,7 +2218,7 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>77</v>
@@ -2220,7 +2232,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
@@ -2229,7 +2241,7 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>79</v>
@@ -2243,7 +2255,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>80</v>
@@ -2252,7 +2264,7 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>81</v>
@@ -2266,7 +2278,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>82</v>
@@ -2275,7 +2287,7 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>83</v>
@@ -2289,7 +2301,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>84</v>
@@ -2298,7 +2310,7 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>85</v>
@@ -2312,19 +2324,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2335,19 +2347,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2358,16 +2370,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>90</v>
@@ -2381,7 +2393,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>91</v>
@@ -2390,7 +2402,7 @@
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>92</v>
@@ -2404,7 +2416,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>93</v>
@@ -2413,7 +2425,7 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>94</v>
@@ -2427,7 +2439,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>95</v>
@@ -2436,7 +2448,7 @@
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>96</v>
@@ -2450,7 +2462,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>97</v>
@@ -2459,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>98</v>
@@ -2473,7 +2485,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -2482,7 +2494,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>100</v>
@@ -2496,7 +2508,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>101</v>
@@ -2505,7 +2517,7 @@
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>102</v>
@@ -2519,7 +2531,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -2528,7 +2540,7 @@
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>104</v>
@@ -2542,7 +2554,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>105</v>
@@ -2551,7 +2563,7 @@
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>106</v>
@@ -2565,7 +2577,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>107</v>
@@ -2574,7 +2586,7 @@
         <v>12</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>108</v>
@@ -2588,16 +2600,16 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>110</v>
@@ -2611,16 +2623,16 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>112</v>
@@ -2634,7 +2646,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>113</v>
@@ -2643,7 +2655,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>114</v>
@@ -2657,16 +2669,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>116</v>
@@ -2680,16 +2692,16 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>118</v>
@@ -2703,7 +2715,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
@@ -2712,7 +2724,7 @@
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>120</v>
@@ -2726,7 +2738,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>121</v>
@@ -2735,7 +2747,7 @@
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>122</v>
@@ -2749,7 +2761,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>123</v>
@@ -2758,7 +2770,7 @@
         <v>12</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>124</v>
@@ -2772,7 +2784,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>125</v>
@@ -2781,7 +2793,7 @@
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>126</v>
@@ -2795,19 +2807,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2818,19 +2830,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="C96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2841,16 +2853,16 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>136</v>
@@ -2864,7 +2876,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>137</v>
@@ -2873,7 +2885,7 @@
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>138</v>
@@ -2887,7 +2899,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>139</v>
@@ -2896,7 +2908,7 @@
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>140</v>
@@ -2910,7 +2922,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>141</v>
@@ -2919,7 +2931,7 @@
         <v>12</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>142</v>
@@ -2933,7 +2945,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>143</v>
@@ -2942,10 +2954,10 @@
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2956,19 +2968,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2979,19 +2991,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -3002,19 +3014,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3025,19 +3037,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3048,7 +3060,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>151</v>
@@ -3057,7 +3069,7 @@
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>152</v>
@@ -3071,7 +3083,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>153</v>
@@ -3080,7 +3092,7 @@
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>154</v>
@@ -3094,19 +3106,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3117,19 +3129,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3140,16 +3152,16 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>136</v>
@@ -3163,7 +3175,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>137</v>
@@ -3172,7 +3184,7 @@
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>138</v>
@@ -3186,7 +3198,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>139</v>
@@ -3195,7 +3207,7 @@
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>140</v>
@@ -3209,7 +3221,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>141</v>
@@ -3218,7 +3230,7 @@
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>142</v>
@@ -3232,7 +3244,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>143</v>
@@ -3241,10 +3253,10 @@
         <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3255,19 +3267,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3278,19 +3290,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3301,19 +3313,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3324,19 +3336,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3347,7 +3359,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>151</v>
@@ -3356,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>152</v>
@@ -3370,7 +3382,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>153</v>
@@ -3379,7 +3391,7 @@
         <v>12</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>154</v>
@@ -3393,19 +3405,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3416,19 +3428,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3439,16 +3451,16 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>164</v>
@@ -3462,7 +3474,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>165</v>
@@ -3471,7 +3483,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>166</v>
@@ -3485,7 +3497,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>167</v>
@@ -3494,7 +3506,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>168</v>
@@ -3508,16 +3520,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>170</v>
@@ -3531,16 +3543,16 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>172</v>
@@ -3554,7 +3566,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>173</v>
@@ -3563,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>174</v>
@@ -3577,7 +3589,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>175</v>
@@ -3586,7 +3598,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>176</v>
@@ -3600,19 +3612,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3623,19 +3635,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="E131" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3646,19 +3658,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3669,7 +3681,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>167</v>
@@ -3678,7 +3690,7 @@
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>168</v>
@@ -3692,16 +3704,16 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>170</v>
@@ -3715,16 +3727,16 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>172</v>
@@ -3738,7 +3750,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>173</v>
@@ -3747,7 +3759,7 @@
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>174</v>
@@ -3761,7 +3773,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>175</v>
@@ -3770,7 +3782,7 @@
         <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>176</v>
@@ -3784,19 +3796,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="C138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -3807,24 +3819,70 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="B140" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" s="2" t="s">
+      <c r="E140" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>27</v>
       </c>
     </row>
